--- a/从零开始学Slots/从零开始学Slots-23-基础篇-StickyWild.xlsx
+++ b/从零开始学Slots/从零开始学Slots-23-基础篇-StickyWild.xlsx
@@ -6327,6 +6327,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J148" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6861,5 +6864,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:U64" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-23-基础篇-StickyWild.xlsx
+++ b/从零开始学Slots/从零开始学Slots-23-基础篇-StickyWild.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="182">
   <si>
     <r>
       <rPr>
@@ -5365,7 +5365,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5472,6 +5472,14 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6219,8 +6227,8 @@
       <c r="A106" s="7"/>
     </row>
     <row r="107" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="5" t="s">
-        <v>81</v>
+      <c r="A107" s="27">
+        <v>1</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6704,8 +6712,8 @@
       <c r="D33" s="14"/>
     </row>
     <row r="34" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
-        <v>164</v>
+      <c r="A34" s="28">
+        <v>0</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>165</v>
@@ -6716,8 +6724,8 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
-        <v>166</v>
+      <c r="A35" s="28">
+        <v>1</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>167</v>
@@ -6728,8 +6736,8 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
-        <v>168</v>
+      <c r="A36" s="28">
+        <v>2</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>169</v>
@@ -6740,8 +6748,8 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15" t="s">
-        <v>170</v>
+      <c r="A37" s="28">
+        <v>3</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>171</v>
@@ -6752,8 +6760,8 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15" t="s">
-        <v>172</v>
+      <c r="A38" s="28">
+        <v>4</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>173</v>
@@ -6764,8 +6772,8 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15" t="s">
-        <v>174</v>
+      <c r="A39" s="28">
+        <v>5</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>175</v>
